--- a/artfynd/A 41001-2026 artfynd.xlsx
+++ b/artfynd/A 41001-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759804</v>
       </c>
       <c r="B2" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41001-2026 artfynd.xlsx
+++ b/artfynd/A 41001-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759804</v>
       </c>
       <c r="B2" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41001-2026 artfynd.xlsx
+++ b/artfynd/A 41001-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759804</v>
       </c>
       <c r="B2" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41001-2026 artfynd.xlsx
+++ b/artfynd/A 41001-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759804</v>
       </c>
       <c r="B2" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41001-2026 artfynd.xlsx
+++ b/artfynd/A 41001-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759804</v>
       </c>
       <c r="B2" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41001-2026 artfynd.xlsx
+++ b/artfynd/A 41001-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759804</v>
       </c>
       <c r="B2" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41001-2026 artfynd.xlsx
+++ b/artfynd/A 41001-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759804</v>
       </c>
       <c r="B2" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41001-2026 artfynd.xlsx
+++ b/artfynd/A 41001-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759804</v>
       </c>
       <c r="B2" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41001-2026 artfynd.xlsx
+++ b/artfynd/A 41001-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136759804</v>
+        <v>137441595</v>
       </c>
       <c r="B2" t="n">
-        <v>80628</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grundvattnet, Nb</t>
+          <t>Storberget, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741240</v>
+        <v>741428</v>
       </c>
       <c r="R2" t="n">
-        <v>7305181</v>
+        <v>7305061</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,27 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,24 +775,603 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137441595</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137441603</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91186</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>741108</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7305272</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137441603</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137441590</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79533</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>741586</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7304808</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137441590</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137441594</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79533</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>741439</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7305064</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137441594</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136759804</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80628</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grundvattnet, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>741240</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7305181</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136759804</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137441599</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>741316</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7305131</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fodersök</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137441599</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41001-2026 artfynd.xlsx
+++ b/artfynd/A 41001-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137441595</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137441603</v>
       </c>
       <c r="B3" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137441590</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137441594</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41001-2026 artfynd.xlsx
+++ b/artfynd/A 41001-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137441595</v>
+        <v>137433513</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92928</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>757</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storberget, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741428</v>
+        <v>741625</v>
       </c>
       <c r="R2" t="n">
-        <v>7305061</v>
+        <v>7304793</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,42 +763,43 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137441595</t>
+          <t>https://artportalen.se/Sighting/137433513</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137441603</v>
+        <v>137433517</v>
       </c>
       <c r="B3" t="n">
-        <v>91189</v>
+        <v>79614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741108</v>
+        <v>741554</v>
       </c>
       <c r="R3" t="n">
-        <v>7305272</v>
+        <v>7304862</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,49 +891,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137441603</t>
+          <t>https://artportalen.se/Sighting/137433517</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137441590</v>
+        <v>137441595</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741586</v>
+        <v>741428</v>
       </c>
       <c r="R4" t="n">
-        <v>7304808</v>
+        <v>7305061</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,38 +1014,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137441590</t>
+          <t>https://artportalen.se/Sighting/137441595</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137441594</v>
+        <v>137433519</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>83403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1055,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741439</v>
+        <v>741551</v>
       </c>
       <c r="R5" t="n">
-        <v>7305064</v>
+        <v>7304863</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1115,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137441594</t>
+          <t>https://artportalen.se/Sighting/137433519</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136759804</v>
+        <v>137441603</v>
       </c>
       <c r="B6" t="n">
-        <v>80628</v>
+        <v>91189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,38 +1143,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grundvattnet, Nb</t>
+          <t>Storberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741240</v>
+        <v>741108</v>
       </c>
       <c r="R6" t="n">
-        <v>7305181</v>
+        <v>7305272</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1197,27 +1197,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,27 +1227,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759804</t>
+          <t>https://artportalen.se/Sighting/137441603</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137441599</v>
+        <v>137433570</v>
       </c>
       <c r="B7" t="n">
-        <v>58032</v>
+        <v>96649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741316</v>
+        <v>741214</v>
       </c>
       <c r="R7" t="n">
-        <v>7305131</v>
+        <v>7305143</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1319,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Fodersök</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,18 +1339,3184 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137433570</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137433531</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96646</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>741436</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7305061</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433531</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137433569</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92581</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>741208</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7305147</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433569</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137433515</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93485</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>741604</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7304829</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433515</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137433510</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79535</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>741616</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7304775</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433510</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137433514</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79535</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>741599</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7304794</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433514</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137433518</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79535</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>741553</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7304861</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433518</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137433522</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79535</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>741454</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7304919</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433522</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137433533</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79535</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>741424</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7305066</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433533</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137433553</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79535</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>741104</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7305262</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433553</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137433557</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79535</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>741044</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7305220</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433557</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137441590</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79535</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>741586</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7304808</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137441590</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137441594</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79535</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>741439</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7305064</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137441594</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137433552</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79559</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>741129</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7305230</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433552</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137433511</v>
+      </c>
+      <c r="B21" t="n">
+        <v>83526</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>741610</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7304767</v>
+      </c>
+      <c r="S21" t="n">
+        <v>19</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433511</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137433537</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80544</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>741362</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7305081</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433537</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136759804</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80628</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Grundvattnet, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>741240</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7305181</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136759804</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137433521</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80650</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>741454</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7304919</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433521</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137433523</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80650</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>741451</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7304921</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433523</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137433529</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80650</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>741440</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7305050</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433529</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137433530</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80655</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>741440</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7305050</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433530</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137433509</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57946</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100011</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kungsörn</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Aquila chrysaetos</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>741726</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7305083</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433509</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137441599</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>741316</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7305131</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Fodersök</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137441599</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137433527</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99434</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>741441</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7305003</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433527</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137433528</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99434</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>741434</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7305046</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433528</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137433551</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98302</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>741133</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7305228</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433551</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137433539</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98296</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>741362</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7305081</v>
+      </c>
+      <c r="S33" t="n">
+        <v>7</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433539</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137433512</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78540</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>741620</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7304775</v>
+      </c>
+      <c r="S34" t="n">
+        <v>16</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433512</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137433520</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79558</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Storberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>741489</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7304893</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433520</t>
         </is>
       </c>
     </row>
@@ -1372,6 +4528,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41001-2026 artfynd.xlsx
+++ b/artfynd/A 41001-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137433513</v>
       </c>
       <c r="B2" t="n">
-        <v>92928</v>
+        <v>92932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137433517</v>
       </c>
       <c r="B3" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137441595</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137433519</v>
       </c>
       <c r="B5" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137441603</v>
       </c>
       <c r="B6" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>137433570</v>
       </c>
       <c r="B7" t="n">
-        <v>96649</v>
+        <v>96653</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137433531</v>
       </c>
       <c r="B8" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137433569</v>
       </c>
       <c r="B9" t="n">
-        <v>92581</v>
+        <v>92585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137433515</v>
       </c>
       <c r="B10" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137433510</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137433514</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137433518</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137433522</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137433533</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137433553</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137433557</v>
       </c>
       <c r="B17" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>137441590</v>
       </c>
       <c r="B18" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>137441594</v>
       </c>
       <c r="B19" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>137433552</v>
       </c>
       <c r="B20" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>137433511</v>
       </c>
       <c r="B21" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>137433537</v>
       </c>
       <c r="B22" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>137433521</v>
       </c>
       <c r="B24" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>137433523</v>
       </c>
       <c r="B25" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>137433529</v>
       </c>
       <c r="B26" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>137433530</v>
       </c>
       <c r="B27" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>137433509</v>
       </c>
       <c r="B28" t="n">
-        <v>57946</v>
+        <v>57949</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>137441599</v>
       </c>
       <c r="B29" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>137433527</v>
       </c>
       <c r="B30" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137433528</v>
       </c>
       <c r="B31" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>137433551</v>
       </c>
       <c r="B32" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>137433539</v>
       </c>
       <c r="B33" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>137433512</v>
       </c>
       <c r="B34" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>137433520</v>
       </c>
       <c r="B35" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
